--- a/EcoReport/template.xlsx
+++ b/EcoReport/template.xlsx
@@ -1,34 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EcoRenSource_20251010\EcoRen_MainForm\EcoRen_MainForm\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aiko\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26E0E63-2AB0-45D2-8C05-51F300266FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5D6AAF1F-4B7F-4AAA-AEAA-0F1FAF95F588}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="template" sheetId="8" r:id="rId1"/>
+    <sheet name="計算例" sheetId="7" r:id="rId1"/>
+    <sheet name="部材別" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">template!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">計算例!$A$1:$Q$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">部材別!$A$1:$Q$39</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="116">
   <si>
     <t>工事名称</t>
     <rPh sb="0" eb="2">
@@ -37,6 +47,51 @@
     <rPh sb="2" eb="4">
       <t>メイショウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エコレン計算例</t>
+    <rPh sb="4" eb="7">
+      <t>ケイサンレイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>条件：</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>開孔径φ</t>
+    <rPh sb="0" eb="1">
+      <t>ヒラキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>アナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -115,13 +170,141 @@
         <vertAlign val="subscript"/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
       <t>D</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min/β</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>設計せん断力</t>
+    <rPh sb="0" eb="2">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ダンリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　　両端曲げ降伏</t>
+    <rPh sb="2" eb="4">
+      <t>リョウタン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　　荒川min</t>
+    <rPh sb="2" eb="4">
+      <t>アラカワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　　設計せん断力</t>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ダンリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エコレンの算出</t>
+    <rPh sb="5" eb="7">
+      <t>サンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただし　ΣPw＝ePw + sPw</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>開孔梁のせん断耐力</t>
+    <rPh sb="0" eb="1">
+      <t>ヒラキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>アナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハリ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タイリョク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -165,7 +348,7 @@
         <vertAlign val="subscript"/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -176,7 +359,7 @@
       <rPr>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -252,7 +435,7 @@
         <vertAlign val="superscript"/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -263,7 +446,7 @@
       <rPr>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -281,7 +464,7 @@
         <vertAlign val="subscript"/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -299,7 +482,7 @@
         <vertAlign val="subscript"/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -310,7 +493,7 @@
       <rPr>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -322,7 +505,7 @@
         <vertAlign val="subscript"/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -333,6 +516,40 @@
   </si>
   <si>
     <t>本数-径</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>本数-径</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>梁記号:</t>
+    <rPh sb="0" eb="1">
+      <t>ハリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>キゴウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>[階:</t>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>]</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -349,6 +566,35 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <r>
+      <t>uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uτHとして</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>b(㎜)</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -361,6 +607,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>dc(㎜)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>C(㎜)</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -370,18 +620,3744 @@
   </si>
   <si>
     <t>Fc(N/㎟)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>strListName</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BodyWidth</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BodyHeight</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>span_d</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>span_dc</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>rangeC_C</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Fc</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Uchinori</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Qo</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>min(shukyoku_QSU_B,shukyoku_Qm_B)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LeftHiCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mainDm</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LeftLowCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mainDm</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RightHiCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mainDm</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RightLowCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mainDm</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mainKind</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stpCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stpDm</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>stpPitch</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>span_max_Pt</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shukyoku_Pw</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>design_sendan_max_Qmu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>design_sendan_MQd2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>design_sendan_tmu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shukyoku_design_sendan_tmin</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>min(design_sendan_tmu,shukyoku_design_sendan_tmin)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>min(design_sendan_tmu,shukyoku_design_sendan_tmin)/min(shukyoku_QSU_B,shukyoku_Qm_B)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>Pt=(at/(b･d))/100=(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_right_Count</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_right_S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>))･</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_max_Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  (%) </t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>Pw=aw/(b･x)=(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stpCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sendan_hokyo_S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stpPitch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Pw</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>ΣMy=上My+下My=上(0.9･at･1.1･σy･d)+下(0.9･at･1.1･σy･d)=0.9･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_left_at</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000)･1.1･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mainKind</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000)+0.9･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_right_at</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000)･1.1･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mainKind</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_LowMy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_My</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_HiMy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(kN・m)</t>
+    </r>
+    <rPh sb="4" eb="5">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>My=MAX(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_LowMy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_My</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_max_My</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(kN･m)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>M/Qd=maxMy/(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Qm･d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_max_My</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_max_Qmu</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000))=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_MQd2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　(1≦M/Q･ｄ≦3)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C=D/2-dc= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyHeight</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2･ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_dc</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (㎜)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>sPw=saw/(b･C区間)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_Cst</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stpCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sendan_hokyo_S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_S_hokyou_sPw</t>
+    </r>
+    <rPh sb="12" eb="14">
+      <t>クカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>τｍu=Qm/(b･j)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_max_Qmu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_tmu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (N/㎟)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(ｂ･j)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_design_sendan_Qmin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_design_sendan_tmin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (N/㎟)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>needs_danmen_shukyoku_mage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>sPw=(nS･aw)/(b･c) = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_Cst</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sendan_hokyo_S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stpCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>))/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_S_hokyou_sPw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　（C区間St=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_Cst</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>組）</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>ePa=ePw</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･b･C=-0.00133･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rangeC_C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>needs_danmen_shukyoku_mage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (㎟)　　エコレンの補強必要断面積</t>
+    </r>
+    <rPh sb="77" eb="79">
+      <t>ホキョウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="81" eb="84">
+      <t>ダンメンセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_utH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N/㎟)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>uτH ≦ uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_utD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ≦ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_utH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　OK</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>※</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=0.053･Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･(Fc+18)･(1-1.16･H/D)/[(M/Q･d)+0.12]+0.85･(ePw･eσy +</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pw･sσy)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>ePw</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=〔{[(uτD/β)－0.053･Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･(Fc+18)･(1-1.16･H/D)/(M/Qd)+0.12]/0.85}</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>－(</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pw･sσy)〕/eσy　　</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>uτH=0.053･Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･(Fc+18)･(1-1.16･H/D))/(M/Qd+0.12)+0.85･(ePw･eσy +</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pw･sσy)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>Qm=Qo＋n･ΣMy/l'=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Qo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_HiMy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Uchinori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_max_Qmu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (kN)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{0.053･Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･(Fc+18)/[(M/Qd)+0.12]+0.85･(Pw･sσy)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}･ｂ･j={[0.053･</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_max_Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+18))/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_MQd2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0.12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0.85･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Pw</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stpKind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/1000=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_design_sendan_Qmin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (kN)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        =〔{[(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min(design_sendan_tmu,shukyoku_design_sendan_tmin)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min(shukyoku_QSU_B,shukyoku_Qm_B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)－0.053･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_max_Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+18)･(1-1.61･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>セル[A2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyHeight</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_MQd2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0.12)]/0.85}</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_S_hokyou_sPw</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_S_hokyou_wft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)〕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>セル[D2]</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        =0.053･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>span_max_Pt</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+18)･(1-1.61･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>セル[A2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyHeight</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_MQd2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0.12)+0.85･(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_ePw</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>セル[D2]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_S_hokyou_sPw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_S_hokyou_wft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min(τmu、uτ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)=mim (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_tmu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_design_sendan_tmin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>design_sendan_tmu,shukyoku_design_sendan_tmin)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = uτH･ｂ･j =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_utH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BodyWidth</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>･</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">span_j </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_utH･BodyWidth･span_j</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(kN)</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ≦ Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H　　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min(design_sendan_tmu,shukyoku_design_sendan_tmin)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ≦ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_utH･BodyWidth･span_j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>strFloor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PAI</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>needs_danmen_shukyoku_mage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(㎟) ≦</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku_Qm_S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>㎟ 　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">エコレン </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shukyoku</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　　OK</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>strFloor：</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -389,14 +4365,14 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -405,7 +4381,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -414,7 +4390,7 @@
       <vertAlign val="superscript"/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -423,35 +4399,96 @@
       <vertAlign val="subscript"/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <color rgb="FF00B0F0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -546,90 +4583,153 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -648,8 +4748,380 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>224518</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>115660</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>537482</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>102052</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C0DC2CD-19FD-4B9C-9786-534D4C06F744}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6615793" y="115660"/>
+          <a:ext cx="3322864" cy="329292"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>計算が成立した最小行、最小開口径で実行する</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>34018</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>34019</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>149677</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="右中かっこ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92DEC0D2-16FB-4B0F-A5CF-38BDAC217D20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7812543" y="-1077006"/>
+          <a:ext cx="287108" cy="4223658"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>179613</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>29935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>612322</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="テキスト ボックス 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CB7018C-48AA-44EE-8465-17D045DBBCA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6540952" y="1220560"/>
+          <a:ext cx="3433084" cy="249012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+            <a:t>mainDm,mainKind,stpDm,stpPitch</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>に関しては、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+            <a:t>prefix</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>を含む</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>472168</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>81642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>306162</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>6804</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4741B65-6E03-45FD-A763-89E310A58845}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9146722" y="2292803"/>
+          <a:ext cx="2582636" cy="775608"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>変数名不明</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>セル</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+            <a:t>[A2]=</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>検証内径</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>セル</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>[D2]=</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>エコレン素材強度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>対象素材強度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -944,337 +5416,1569 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72618692-0D7E-44DA-89A4-5D3C7ACB16C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:Q56"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="1" customWidth="1"/>
-    <col min="2" max="15" width="7.125" style="1" customWidth="1"/>
-    <col min="16" max="17" width="7.125" customWidth="1"/>
+    <col min="1" max="15" width="7.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="13.15" customHeight="1">
+    <row r="1" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="15"/>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
       <c r="P1" s="1"/>
-      <c r="Q1" s="5"/>
-    </row>
-    <row r="2" spans="1:17" ht="12.75" customHeight="1">
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="40"/>
+    </row>
+    <row r="5" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+    </row>
+    <row r="19" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+    </row>
+    <row r="25" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+    </row>
+    <row r="26" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+    </row>
+    <row r="27" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+    </row>
+    <row r="28" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+    </row>
+    <row r="29" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" spans="16:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" spans="16:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" spans="16:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" spans="16:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" spans="16:17" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="P54"/>
+      <c r="Q54"/>
+    </row>
+    <row r="56" spans="16:17" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="P56"/>
+      <c r="Q56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="P4:Q4"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="89" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q39"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.25" style="17" customWidth="1"/>
+    <col min="2" max="15" width="7.125" style="17" customWidth="1"/>
+    <col min="16" max="17" width="7.125" style="19" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+    </row>
+    <row r="3" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="47"/>
+    </row>
+    <row r="4" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="23"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="28"/>
+    </row>
+    <row r="5" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+    </row>
+    <row r="6" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="30"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+    </row>
+    <row r="7" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="I7" s="41"/>
+      <c r="J7" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="K7" s="41"/>
+      <c r="L7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="M7" s="41"/>
+      <c r="N7" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="O7" s="41"/>
+      <c r="P7" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q7" s="41"/>
+    </row>
+    <row r="8" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="43"/>
+    </row>
+    <row r="9" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+    </row>
+    <row r="10" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+    </row>
+    <row r="11" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+    </row>
+    <row r="12" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+    </row>
+    <row r="13" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="45"/>
+    </row>
+    <row r="14" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+    </row>
+    <row r="16" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="P16" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="47"/>
+    </row>
+    <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="28"/>
+    </row>
+    <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+    </row>
+    <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="30"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+    </row>
+    <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="Q20" s="41"/>
+    </row>
+    <row r="21" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="43"/>
+    </row>
+    <row r="22" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+    </row>
+    <row r="23" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+    </row>
+    <row r="24" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+    </row>
+    <row r="25" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+    </row>
+    <row r="26" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+    </row>
+    <row r="27" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="18"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+    </row>
+    <row r="29" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="N29" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="P29" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="47"/>
+    </row>
+    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="23"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="28"/>
+    </row>
+    <row r="31" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="21"/>
-    </row>
-    <row r="4" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="3" t="s">
+      <c r="H31" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+    </row>
+    <row r="32" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="30"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+    </row>
+    <row r="33" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="23"/>
-    </row>
-    <row r="5" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-    </row>
-    <row r="6" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-    </row>
-    <row r="7" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q7" s="19"/>
-    </row>
-    <row r="8" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="26"/>
-    </row>
-    <row r="9" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-    </row>
-    <row r="10" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-    </row>
-    <row r="11" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A11" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-    </row>
-    <row r="12" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-    </row>
-    <row r="13" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-    </row>
-    <row r="14" spans="1:17" ht="10.5" customHeight="1"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q33" s="41"/>
+    </row>
+    <row r="34" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="43"/>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
+    </row>
+    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="44"/>
+      <c r="P36" s="44"/>
+      <c r="Q36" s="44"/>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="44"/>
+    </row>
+    <row r="38" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="44"/>
+      <c r="N38" s="44"/>
+      <c r="O38" s="44"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="44"/>
+    </row>
+    <row r="39" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="45"/>
+      <c r="P39" s="45"/>
+      <c r="Q39" s="45"/>
+    </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="171">
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="P39:Q39"/>
     <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
     <mergeCell ref="N13:O13"/>
     <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:G13"/>
@@ -1332,6 +7036,6 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>